--- a/output/pdf_financials_xlsx/GH.xlsx
+++ b/output/pdf_financials_xlsx/GH.xlsx
@@ -912,7 +912,7 @@
         <v>-0.851091</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-2.984706</v>
+        <v>-8.861065999999999</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1024,7 +1024,7 @@
         <v>-7.252581</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.93818</v>
+        <v>-2.93818</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>-7.252581</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.93818</v>
+        <v>-2.93818</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>-13.29520158588079</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>50.39276460833452</v>
+        <v>149.6072353916655</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>-93.20305741167108</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>34.55542430473524</v>
+        <v>-34.55542430473524</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>-7.252581</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>2.93818</v>
+        <v>-2.93818</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>-7.252581</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>2.93818</v>
+        <v>-2.93818</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GH.xlsx
+++ b/output/pdf_financials_xlsx/GH.xlsx
@@ -1504,25 +1504,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>9.973895000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>14.572108</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>15.6145</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>13.9792</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>14.3936</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>15.1584</v>
       </c>
     </row>
     <row r="35">
@@ -1560,25 +1560,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>9.973895000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>14.572108</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>15.6145</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>13.9792</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>14.3936</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>15.1584</v>
       </c>
     </row>
     <row r="37">
@@ -1896,25 +1896,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>10.216873</v>
+        <v>0.242978</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>14.86888</v>
+        <v>0.296772</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>17.2</v>
+        <v>1.6</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>17.2226</v>
+        <v>1.6081</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>15.5138</v>
+        <v>1.5346</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>15.8308</v>
+        <v>1.4372</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>16.6818</v>
+        <v>1.5234</v>
       </c>
     </row>
     <row r="49">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">

--- a/output/pdf_financials_xlsx/GH.xlsx
+++ b/output/pdf_financials_xlsx/GH.xlsx
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0</v>
+        <v>57.890798</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>4.202951</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>4.202951</v>
+        <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0</v>
